--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/DELAWARE_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/DELAWARE_2013.xlsx
@@ -1615,7 +1615,7 @@
         <v>19</v>
       </c>
       <c r="D70">
-        <v>0.009978991596639</v>
+        <v>0.009978991596639002</v>
       </c>
     </row>
     <row r="71">
@@ -5053,7 +5053,7 @@
         <v>18</v>
       </c>
       <c r="D261">
-        <v>0.009453781512605</v>
+        <v>0.009453781512605001</v>
       </c>
     </row>
     <row r="262">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C286">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C402">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C445">
